--- a/Document/客户方案计算表.xlsx
+++ b/Document/客户方案计算表.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sun-Jackey\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70784827-2EE7-4867-AB99-2FB650EE5997}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19271" windowHeight="8820" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="客户方案计算表" sheetId="1" r:id="rId1"/>
@@ -18,14 +12,7 @@
     <sheet name="减免计算" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -455,6 +442,12 @@
     <t>结果</t>
   </si>
   <si>
+    <t>减免最小值</t>
+  </si>
+  <si>
+    <t>减免最大值</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -754,15 +747,43 @@
     </r>
   </si>
   <si>
-    <t>减免最小值</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>减免最大值</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>最大减免</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=合同金额-已还金额-剩余本金
+合同金额=每期还款*总期数
+已还金额=每期还款*还款期数
+当期剩余本金=实际到账金额-应付利息-冲销本金
+当期应付利息=剩余本金*24%/12
+剩余本金需要逐笔核减计算得出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>最小减免</t>
     </r>
     <r>
@@ -782,39 +803,21 @@
 当期剩余法定利息=剩余本金*17%/12
 剩余本金需要逐笔核减计算得出</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>最大减免</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=合同金额-已还金额-剩余本金
-合同金额=每期还款*总期数
-已还金额=每期还款*还款期数
-当期剩余本金=实际到账金额-应付利息-冲销本金
-当期应付利息=剩余本金*24%/12
-剩余本金需要逐笔核减计算得出</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -839,13 +842,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
@@ -862,17 +858,131 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -880,12 +990,26 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -894,7 +1018,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79995117038483843"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.799951170384838"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -912,12 +1042,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1138,23 +1448,265 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1163,43 +1715,58 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1208,10 +1775,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1223,52 +1799,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1277,78 +1853,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1635,1485 +2213,1484 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:Q49"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="25"/>
-    <col min="2" max="2" width="11.44140625" style="3"/>
-    <col min="3" max="3" width="14" style="25" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" style="3"/>
-    <col min="5" max="5" width="13.6640625" style="25" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="3"/>
-    <col min="7" max="7" width="3.44140625" style="25" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14" style="25" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="9" style="33"/>
+    <col min="2" max="2" width="11.4444444444444" style="3"/>
+    <col min="3" max="3" width="14" style="33" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="3"/>
+    <col min="5" max="5" width="13.6666666666667" style="33" customWidth="1"/>
+    <col min="6" max="6" width="12.6666666666667" style="3"/>
+    <col min="7" max="7" width="3.44444444444444" style="33" customWidth="1"/>
+    <col min="8" max="8" width="11.6666666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14" style="33" customWidth="1"/>
+    <col min="10" max="10" width="10.4444444444444" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.6666666666667" style="33" customWidth="1"/>
     <col min="12" max="13" width="9" style="3"/>
-    <col min="14" max="14" width="37.77734375" style="25" customWidth="1"/>
-    <col min="15" max="15" width="31.109375" style="25" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="25"/>
+    <col min="14" max="14" width="37.7777777777778" style="33" customWidth="1"/>
+    <col min="15" max="15" width="31.1111111111111" style="33" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="44" t="s">
+    <row r="1" spans="2:13">
+      <c r="B1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="H1" s="44" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="H1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="40"/>
-    </row>
-    <row r="2" spans="1:17" ht="72" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="48"/>
+    </row>
+    <row r="2" ht="72" spans="1:13">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="L2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="41"/>
-    </row>
-    <row r="3" spans="1:17" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="B3" s="27" t="s">
+      <c r="M2" s="49"/>
+    </row>
+    <row r="3" ht="28.8" spans="2:17">
+      <c r="B3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="30" t="s">
+      <c r="K3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="27"/>
-      <c r="N3" s="30" t="s">
+      <c r="M3" s="37"/>
+      <c r="N3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-    </row>
-    <row r="4" spans="1:17" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="B4" s="32">
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+    </row>
+    <row r="4" ht="28.8" spans="2:15">
+      <c r="B4" s="40">
         <v>150000</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="41">
         <v>1</v>
       </c>
-      <c r="D4" s="34">
+      <c r="D4" s="42">
         <f>B4*24%/12</f>
         <v>3000</v>
       </c>
-      <c r="E4" s="35">
-        <v>6108.08</v>
-      </c>
-      <c r="F4" s="34">
+      <c r="E4" s="43">
+        <v>6108.08</v>
+      </c>
+      <c r="F4" s="42">
         <f>E4-D4</f>
         <v>3108.08</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="40">
         <v>115967.391155135</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="41">
         <v>11</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="42">
         <f>H4*17%/12</f>
-        <v>1642.8713746977462</v>
-      </c>
-      <c r="K4" s="35">
-        <v>6108.08</v>
-      </c>
-      <c r="L4" s="34">
+        <v>1642.87137469775</v>
+      </c>
+      <c r="K4" s="43">
+        <v>6108.08</v>
+      </c>
+      <c r="L4" s="42">
         <f>K4-J4</f>
-        <v>4465.2086253022535</v>
-      </c>
-      <c r="M4" s="34"/>
-      <c r="N4" s="33" t="s">
+        <v>4465.20862530225</v>
+      </c>
+      <c r="M4" s="42"/>
+      <c r="N4" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="O4" s="33"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="34">
+      <c r="O4" s="41"/>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="B5" s="42">
         <f>B4-F4</f>
-        <v>146891.92000000001</v>
-      </c>
-      <c r="C5" s="33">
+        <v>146891.92</v>
+      </c>
+      <c r="C5" s="41">
         <v>2</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="42">
         <f t="shared" ref="D5:D39" si="0">B5*24%/12</f>
-        <v>2937.8384000000001</v>
-      </c>
-      <c r="E5" s="36">
+        <v>2937.8384</v>
+      </c>
+      <c r="E5" s="44">
         <f>$E$4</f>
         <v>6108.08</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="42">
         <f t="shared" ref="F5:F23" si="1">E5-D5</f>
-        <v>3170.2415999999998</v>
-      </c>
-      <c r="H5" s="34">
+        <v>3170.2416</v>
+      </c>
+      <c r="H5" s="42">
         <f>H4-L4</f>
-        <v>111502.18252983275</v>
-      </c>
-      <c r="I5" s="33">
+        <v>111502.182529833</v>
+      </c>
+      <c r="I5" s="41">
         <v>12</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="42">
         <f t="shared" ref="J5:J39" si="2">H5*17%/12</f>
-        <v>1579.614252505964</v>
-      </c>
-      <c r="K5" s="36">
+        <v>1579.61425250596</v>
+      </c>
+      <c r="K5" s="44">
         <f>$E$4</f>
         <v>6108.08</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="42">
         <f t="shared" ref="L5:L29" si="3">K5-J5</f>
-        <v>4528.4657474940359</v>
-      </c>
-      <c r="M5" s="34"/>
-      <c r="N5" s="37" t="s">
+        <v>4528.46574749404</v>
+      </c>
+      <c r="M5" s="42"/>
+      <c r="N5" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="37" t="s">
+      <c r="O5" s="45" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B6" s="34">
+    <row r="6" spans="2:15">
+      <c r="B6" s="42">
         <f t="shared" ref="B6:B14" si="4">B5-F5</f>
         <v>143721.6784</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="41">
         <v>3</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="42">
         <f t="shared" si="0"/>
-        <v>2874.4335679999999</v>
-      </c>
-      <c r="E6" s="36">
+        <v>2874.433568</v>
+      </c>
+      <c r="E6" s="44">
         <f t="shared" ref="E6:E15" si="5">$E$4</f>
         <v>6108.08</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="42">
         <f t="shared" si="1"/>
         <v>3233.646432</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="42">
         <f t="shared" ref="H6:H29" si="6">H5-L5</f>
-        <v>106973.71678233871</v>
-      </c>
-      <c r="I6" s="33">
+        <v>106973.716782339</v>
+      </c>
+      <c r="I6" s="41">
         <v>13</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="42">
         <f t="shared" si="2"/>
-        <v>1515.4609877497985</v>
-      </c>
-      <c r="K6" s="36">
+        <v>1515.4609877498</v>
+      </c>
+      <c r="K6" s="44">
         <f t="shared" ref="K6:K29" si="7">$E$4</f>
         <v>6108.08</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="42">
         <f t="shared" si="3"/>
-        <v>4592.6190122502012</v>
-      </c>
-      <c r="M6" s="34"/>
-      <c r="N6" s="33" t="s">
+        <v>4592.6190122502</v>
+      </c>
+      <c r="M6" s="42"/>
+      <c r="N6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="O6" s="33"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="34">
+      <c r="O6" s="41"/>
+    </row>
+    <row r="7" spans="2:15">
+      <c r="B7" s="42">
         <f t="shared" si="4"/>
         <v>140488.031968</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="41">
         <v>4</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="42">
         <f t="shared" si="0"/>
-        <v>2809.7606393599999</v>
-      </c>
-      <c r="E7" s="36">
+        <v>2809.76063936</v>
+      </c>
+      <c r="E7" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="42">
         <f t="shared" si="1"/>
         <v>3298.31936064</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="42">
         <f t="shared" si="6"/>
-        <v>102381.09777008851</v>
-      </c>
-      <c r="I7" s="33">
+        <v>102381.097770089</v>
+      </c>
+      <c r="I7" s="41">
         <v>14</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="42">
         <f t="shared" si="2"/>
-        <v>1450.3988850762541</v>
-      </c>
-      <c r="K7" s="36">
+        <v>1450.39888507625</v>
+      </c>
+      <c r="K7" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="42">
         <f t="shared" si="3"/>
-        <v>4657.6811149237456</v>
-      </c>
-      <c r="M7" s="34"/>
-      <c r="N7" s="33" t="s">
+        <v>4657.68111492375</v>
+      </c>
+      <c r="M7" s="42"/>
+      <c r="N7" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="33"/>
-    </row>
-    <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="34">
+      <c r="O7" s="41"/>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="2:15">
+      <c r="B8" s="42">
         <f t="shared" si="4"/>
-        <v>137189.71260736001</v>
-      </c>
-      <c r="C8" s="33">
+        <v>137189.71260736</v>
+      </c>
+      <c r="C8" s="41">
         <v>5</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="42">
         <f t="shared" si="0"/>
         <v>2743.7942521472</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="42">
         <f t="shared" si="1"/>
-        <v>3364.2857478527999</v>
-      </c>
-      <c r="H8" s="34">
+        <v>3364.2857478528</v>
+      </c>
+      <c r="H8" s="42">
         <f t="shared" si="6"/>
-        <v>97723.416655164765</v>
-      </c>
-      <c r="I8" s="33">
+        <v>97723.4166551648</v>
+      </c>
+      <c r="I8" s="41">
         <v>15</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="42">
         <f t="shared" si="2"/>
-        <v>1384.415069281501</v>
-      </c>
-      <c r="K8" s="36">
+        <v>1384.4150692815</v>
+      </c>
+      <c r="K8" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="42">
         <f t="shared" si="3"/>
-        <v>4723.6649307184989</v>
-      </c>
-      <c r="M8" s="34"/>
-      <c r="N8" s="33" t="s">
+        <v>4723.6649307185</v>
+      </c>
+      <c r="M8" s="42"/>
+      <c r="N8" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="43"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="34">
+      <c r="O8" s="51"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="B9" s="42">
         <f t="shared" si="4"/>
-        <v>133825.42685950722</v>
-      </c>
-      <c r="C9" s="33">
+        <v>133825.426859507</v>
+      </c>
+      <c r="C9" s="41">
         <v>6</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="42">
         <f t="shared" si="0"/>
-        <v>2676.5085371901446</v>
-      </c>
-      <c r="E9" s="36">
+        <v>2676.50853719014</v>
+      </c>
+      <c r="E9" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="42">
         <f t="shared" si="1"/>
-        <v>3431.5714628098553</v>
-      </c>
-      <c r="H9" s="34">
+        <v>3431.57146280986</v>
+      </c>
+      <c r="H9" s="42">
         <f t="shared" si="6"/>
-        <v>92999.751724446265</v>
-      </c>
-      <c r="I9" s="33">
+        <v>92999.7517244463</v>
+      </c>
+      <c r="I9" s="41">
         <v>16</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="42">
         <f t="shared" si="2"/>
-        <v>1317.496482762989</v>
-      </c>
-      <c r="K9" s="36">
+        <v>1317.49648276299</v>
+      </c>
+      <c r="K9" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="42">
         <f t="shared" si="3"/>
-        <v>4790.5835172370107</v>
-      </c>
-      <c r="M9" s="34"/>
-      <c r="N9" s="37" t="s">
+        <v>4790.58351723701</v>
+      </c>
+      <c r="M9" s="42"/>
+      <c r="N9" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="O9" s="43" t="s">
+      <c r="O9" s="51" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B10" s="34">
+    <row r="10" spans="2:15">
+      <c r="B10" s="42">
         <f t="shared" si="4"/>
-        <v>130393.85539669737</v>
-      </c>
-      <c r="C10" s="33">
+        <v>130393.855396697</v>
+      </c>
+      <c r="C10" s="41">
         <v>7</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="42">
         <f t="shared" si="0"/>
-        <v>2607.8771079339472</v>
-      </c>
-      <c r="E10" s="36">
+        <v>2607.87710793395</v>
+      </c>
+      <c r="E10" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="42">
         <f t="shared" si="1"/>
-        <v>3500.2028920660528</v>
-      </c>
-      <c r="H10" s="34">
+        <v>3500.20289206605</v>
+      </c>
+      <c r="H10" s="42">
         <f t="shared" si="6"/>
-        <v>88209.168207209252</v>
-      </c>
-      <c r="I10" s="33">
+        <v>88209.1682072093</v>
+      </c>
+      <c r="I10" s="41">
         <v>17</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="42">
         <f t="shared" si="2"/>
-        <v>1249.6298829354644</v>
-      </c>
-      <c r="K10" s="36">
+        <v>1249.62988293546</v>
+      </c>
+      <c r="K10" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="42">
         <f t="shared" si="3"/>
-        <v>4858.4501170645353</v>
-      </c>
-      <c r="M10" s="34"/>
-      <c r="N10" s="46" t="s">
+        <v>4858.45011706454</v>
+      </c>
+      <c r="M10" s="42"/>
+      <c r="N10" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="O10" s="47"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="34">
+      <c r="O10" s="41"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="B11" s="42">
         <f t="shared" si="4"/>
-        <v>126893.65250463132</v>
-      </c>
-      <c r="C11" s="33">
+        <v>126893.652504631</v>
+      </c>
+      <c r="C11" s="41">
         <v>8</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="42">
         <f t="shared" si="0"/>
-        <v>2537.8730500926263</v>
-      </c>
-      <c r="E11" s="36">
+        <v>2537.87305009263</v>
+      </c>
+      <c r="E11" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="42">
         <f t="shared" si="1"/>
-        <v>3570.2069499073737</v>
-      </c>
-      <c r="H11" s="34">
+        <v>3570.20694990737</v>
+      </c>
+      <c r="H11" s="42">
         <f t="shared" si="6"/>
-        <v>83350.718090144714</v>
-      </c>
-      <c r="I11" s="33">
+        <v>83350.7180901447</v>
+      </c>
+      <c r="I11" s="41">
         <v>18</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="42">
         <f t="shared" si="2"/>
-        <v>1180.8018396103835</v>
-      </c>
-      <c r="K11" s="36">
+        <v>1180.80183961038</v>
+      </c>
+      <c r="K11" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="42">
         <f t="shared" si="3"/>
-        <v>4927.2781603896165</v>
-      </c>
-      <c r="M11" s="34"/>
-      <c r="N11" s="33" t="s">
+        <v>4927.27816038962</v>
+      </c>
+      <c r="M11" s="42"/>
+      <c r="N11" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="33" t="s">
+      <c r="O11" s="41" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="34">
+    <row r="12" spans="2:13">
+      <c r="B12" s="42">
         <f t="shared" si="4"/>
-        <v>123323.44555472395</v>
-      </c>
-      <c r="C12" s="33">
+        <v>123323.445554724</v>
+      </c>
+      <c r="C12" s="41">
         <v>9</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="42">
         <f t="shared" si="0"/>
-        <v>2466.4689110944787</v>
-      </c>
-      <c r="E12" s="36">
+        <v>2466.46891109448</v>
+      </c>
+      <c r="E12" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="42">
         <f t="shared" si="1"/>
-        <v>3641.6110889055212</v>
-      </c>
-      <c r="H12" s="34">
+        <v>3641.61108890552</v>
+      </c>
+      <c r="H12" s="42">
         <f t="shared" si="6"/>
-        <v>78423.439929755099</v>
-      </c>
-      <c r="I12" s="33">
+        <v>78423.4399297551</v>
+      </c>
+      <c r="I12" s="41">
         <v>19</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="42">
         <f t="shared" si="2"/>
-        <v>1110.9987323381972</v>
-      </c>
-      <c r="K12" s="36">
+        <v>1110.9987323382</v>
+      </c>
+      <c r="K12" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="42">
         <f t="shared" si="3"/>
-        <v>4997.0812676618025</v>
-      </c>
-      <c r="M12" s="40"/>
-    </row>
-    <row r="13" spans="1:17" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="34">
+        <v>4997.0812676618</v>
+      </c>
+      <c r="M12" s="48"/>
+    </row>
+    <row r="13" ht="13.5" customHeight="1" spans="2:15">
+      <c r="B13" s="42">
         <f t="shared" si="4"/>
-        <v>119681.83446581842</v>
-      </c>
-      <c r="C13" s="37">
+        <v>119681.834465818</v>
+      </c>
+      <c r="C13" s="45">
         <v>10</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="42">
         <f t="shared" si="0"/>
-        <v>2393.6366893163681</v>
-      </c>
-      <c r="E13" s="36">
+        <v>2393.63668931637</v>
+      </c>
+      <c r="E13" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="42">
         <f t="shared" si="1"/>
-        <v>3714.4433106836318</v>
-      </c>
-      <c r="H13" s="34">
+        <v>3714.44331068363</v>
+      </c>
+      <c r="H13" s="42">
         <f t="shared" si="6"/>
-        <v>73426.358662093291</v>
-      </c>
-      <c r="I13" s="33">
+        <v>73426.3586620933</v>
+      </c>
+      <c r="I13" s="41">
         <v>20</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="42">
         <f t="shared" si="2"/>
-        <v>1040.2067477129883</v>
-      </c>
-      <c r="K13" s="36">
+        <v>1040.20674771299</v>
+      </c>
+      <c r="K13" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="42">
         <f t="shared" si="3"/>
-        <v>5067.8732522870114</v>
-      </c>
-      <c r="M13" s="40"/>
-      <c r="N13" s="48" t="s">
+        <v>5067.87325228701</v>
+      </c>
+      <c r="M13" s="48"/>
+      <c r="N13" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="O13" s="49"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="38">
+      <c r="O13" s="53"/>
+    </row>
+    <row r="14" spans="2:15">
+      <c r="B14" s="46">
         <f t="shared" si="4"/>
-        <v>115967.39115513478</v>
-      </c>
-      <c r="C14" s="39">
+        <v>115967.391155135</v>
+      </c>
+      <c r="C14" s="47">
         <v>11</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="46">
         <f t="shared" si="0"/>
-        <v>2319.3478231026957</v>
-      </c>
-      <c r="E14" s="39">
+        <v>2319.3478231027</v>
+      </c>
+      <c r="E14" s="47">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="46">
         <f t="shared" si="1"/>
-        <v>3788.7321768973043</v>
-      </c>
-      <c r="H14" s="34">
+        <v>3788.7321768973</v>
+      </c>
+      <c r="H14" s="42">
         <f t="shared" si="6"/>
-        <v>68358.485409806279</v>
-      </c>
-      <c r="I14" s="33">
+        <v>68358.4854098063</v>
+      </c>
+      <c r="I14" s="41">
         <v>21</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="42">
         <f t="shared" si="2"/>
-        <v>968.41187663892242</v>
-      </c>
-      <c r="K14" s="36">
+        <v>968.411876638922</v>
+      </c>
+      <c r="K14" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="42">
         <f t="shared" si="3"/>
-        <v>5139.668123361078</v>
-      </c>
-      <c r="M14" s="40"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="51"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="34">
+        <v>5139.66812336108</v>
+      </c>
+      <c r="M14" s="48"/>
+      <c r="N14" s="54"/>
+      <c r="O14" s="55"/>
+    </row>
+    <row r="15" spans="2:15">
+      <c r="B15" s="42"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="44">
         <f t="shared" si="5"/>
         <v>6108.08</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="42">
         <f t="shared" si="6"/>
-        <v>63218.817286445199</v>
-      </c>
-      <c r="I15" s="33">
+        <v>63218.8172864452</v>
+      </c>
+      <c r="I15" s="41">
         <v>22</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="42">
         <f t="shared" si="2"/>
-        <v>895.59991155797377</v>
-      </c>
-      <c r="K15" s="36">
+        <v>895.599911557974</v>
+      </c>
+      <c r="K15" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="42">
         <f t="shared" si="3"/>
-        <v>5212.4800884420265</v>
-      </c>
-      <c r="M15" s="40"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="51"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="34">
+        <v>5212.48008844203</v>
+      </c>
+      <c r="M15" s="48"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="55"/>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="B16" s="42"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="44">
         <f t="shared" ref="E16:E25" si="8">$E$4</f>
         <v>6108.08</v>
       </c>
-      <c r="F16" s="34">
+      <c r="F16" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="42">
         <f t="shared" si="6"/>
-        <v>58006.337198003173</v>
-      </c>
-      <c r="I16" s="33">
+        <v>58006.3371980032</v>
+      </c>
+      <c r="I16" s="41">
         <v>23</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="42">
         <f t="shared" si="2"/>
-        <v>821.7564436383783</v>
-      </c>
-      <c r="K16" s="36">
+        <v>821.756443638378</v>
+      </c>
+      <c r="K16" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="42">
         <f t="shared" si="3"/>
-        <v>5286.3235563616217</v>
-      </c>
-      <c r="M16" s="40"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="51"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="34"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="34">
+        <v>5286.32355636162</v>
+      </c>
+      <c r="M16" s="48"/>
+      <c r="N16" s="54"/>
+      <c r="O16" s="55"/>
+    </row>
+    <row r="17" spans="2:15">
+      <c r="B17" s="42"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="42">
         <f t="shared" si="6"/>
-        <v>52720.013641641548</v>
-      </c>
-      <c r="I17" s="33">
+        <v>52720.0136416415</v>
+      </c>
+      <c r="I17" s="41">
         <v>24</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="42">
         <f t="shared" si="2"/>
-        <v>746.86685992325522</v>
-      </c>
-      <c r="K17" s="36">
+        <v>746.866859923255</v>
+      </c>
+      <c r="K17" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="42">
         <f t="shared" si="3"/>
-        <v>5361.2131400767448</v>
-      </c>
-      <c r="M17" s="40"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="51"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="34"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="34">
+        <v>5361.21314007674</v>
+      </c>
+      <c r="M17" s="48"/>
+      <c r="N17" s="54"/>
+      <c r="O17" s="55"/>
+    </row>
+    <row r="18" spans="2:15">
+      <c r="B18" s="42"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E18" s="36">
+      <c r="E18" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="42">
         <f t="shared" si="6"/>
-        <v>47358.800501564801</v>
-      </c>
-      <c r="I18" s="33">
+        <v>47358.8005015648</v>
+      </c>
+      <c r="I18" s="41">
         <v>25</v>
       </c>
-      <c r="J18" s="34">
+      <c r="J18" s="42">
         <f t="shared" si="2"/>
-        <v>670.91634043883471</v>
-      </c>
-      <c r="K18" s="36">
+        <v>670.916340438835</v>
+      </c>
+      <c r="K18" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="42">
         <f t="shared" si="3"/>
-        <v>5437.1636595611653</v>
-      </c>
-      <c r="M18" s="40"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="51"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="34"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="34">
+        <v>5437.16365956117</v>
+      </c>
+      <c r="M18" s="48"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="55"/>
+    </row>
+    <row r="19" spans="2:15">
+      <c r="B19" s="42"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="42">
         <f t="shared" si="6"/>
-        <v>41921.636842003638</v>
-      </c>
-      <c r="I19" s="33">
+        <v>41921.6368420036</v>
+      </c>
+      <c r="I19" s="41">
         <v>26</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="42">
         <f t="shared" si="2"/>
-        <v>593.88985526171825</v>
-      </c>
-      <c r="K19" s="36">
+        <v>593.889855261718</v>
+      </c>
+      <c r="K19" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="42">
         <f t="shared" si="3"/>
-        <v>5514.1901447382816</v>
-      </c>
-      <c r="M19" s="40"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="51"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="34"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34">
+        <v>5514.19014473828</v>
+      </c>
+      <c r="M19" s="48"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="55"/>
+    </row>
+    <row r="20" spans="2:15">
+      <c r="B20" s="42"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="42">
         <f t="shared" si="6"/>
-        <v>36407.446697265354</v>
-      </c>
-      <c r="I20" s="33">
+        <v>36407.4466972654</v>
+      </c>
+      <c r="I20" s="41">
         <v>27</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="42">
         <f t="shared" si="2"/>
-        <v>515.77216154459256</v>
-      </c>
-      <c r="K20" s="36">
+        <v>515.772161544593</v>
+      </c>
+      <c r="K20" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="42">
         <f t="shared" si="3"/>
-        <v>5592.3078384554074</v>
-      </c>
-      <c r="M20" s="40"/>
-      <c r="N20" s="52"/>
-      <c r="O20" s="53"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="34"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="34">
+        <v>5592.30783845541</v>
+      </c>
+      <c r="M20" s="48"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="57"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="42"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="42">
         <f t="shared" si="6"/>
-        <v>30815.138858809947</v>
-      </c>
-      <c r="I21" s="33">
+        <v>30815.1388588099</v>
+      </c>
+      <c r="I21" s="41">
         <v>28</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="42">
         <f t="shared" si="2"/>
-        <v>436.54780049980764</v>
-      </c>
-      <c r="K21" s="36">
+        <v>436.547800499808</v>
+      </c>
+      <c r="K21" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="42">
         <f t="shared" si="3"/>
-        <v>5671.5321995001923</v>
-      </c>
-      <c r="M21" s="40"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="34"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34">
+        <v>5671.53219950019</v>
+      </c>
+      <c r="M21" s="48"/>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="42"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E22" s="36">
+      <c r="E22" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="42">
         <f t="shared" si="6"/>
-        <v>25143.606659309757</v>
-      </c>
-      <c r="I22" s="33">
+        <v>25143.6066593098</v>
+      </c>
+      <c r="I22" s="41">
         <v>29</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J22" s="42">
         <f t="shared" si="2"/>
-        <v>356.20109434022157</v>
-      </c>
-      <c r="K22" s="36">
+        <v>356.201094340222</v>
+      </c>
+      <c r="K22" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="42">
         <f t="shared" si="3"/>
-        <v>5751.878905659778</v>
-      </c>
-      <c r="M22" s="40"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="34"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34">
+        <v>5751.87890565978</v>
+      </c>
+      <c r="M22" s="48"/>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="42"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E23" s="36">
+      <c r="E23" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="42">
         <f t="shared" si="1"/>
         <v>6108.08</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="42">
         <f t="shared" si="6"/>
-        <v>19391.727753649979</v>
-      </c>
-      <c r="I23" s="33">
+        <v>19391.72775365</v>
+      </c>
+      <c r="I23" s="41">
         <v>30</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="42">
         <f t="shared" si="2"/>
-        <v>274.71614317670804</v>
-      </c>
-      <c r="K23" s="36">
+        <v>274.716143176708</v>
+      </c>
+      <c r="K23" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="42">
         <f t="shared" si="3"/>
-        <v>5833.3638568232918</v>
-      </c>
-      <c r="M23" s="40"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="34"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="34">
+        <v>5833.36385682329</v>
+      </c>
+      <c r="M23" s="48"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E24" s="36">
+      <c r="E24" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="42">
         <f t="shared" ref="F24:F39" si="9">E24-D24</f>
         <v>6108.08</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="42">
         <f t="shared" si="6"/>
-        <v>13558.363896826686</v>
-      </c>
-      <c r="I24" s="33">
+        <v>13558.3638968267</v>
+      </c>
+      <c r="I24" s="41">
         <v>31</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="42">
         <f t="shared" si="2"/>
-        <v>192.07682187171142</v>
-      </c>
-      <c r="K24" s="36">
+        <v>192.076821871711</v>
+      </c>
+      <c r="K24" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="42">
         <f t="shared" si="3"/>
-        <v>5916.0031781282887</v>
-      </c>
-      <c r="M24" s="40"/>
-      <c r="N24" s="25">
+        <v>5916.00317812829</v>
+      </c>
+      <c r="M24" s="48"/>
+      <c r="N24" s="33">
         <f>36-10</f>
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="34"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="34">
+    <row r="25" spans="2:13">
+      <c r="B25" s="42"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E25" s="36">
+      <c r="E25" s="44">
         <f t="shared" si="8"/>
         <v>6108.08</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="42">
         <f t="shared" si="6"/>
-        <v>7642.3607186983972</v>
-      </c>
-      <c r="I25" s="33">
+        <v>7642.3607186984</v>
+      </c>
+      <c r="I25" s="41">
         <v>32</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="42">
         <f t="shared" si="2"/>
-        <v>108.26677684822731</v>
-      </c>
-      <c r="K25" s="36">
+        <v>108.266776848227</v>
+      </c>
+      <c r="K25" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="42">
         <f t="shared" si="3"/>
-        <v>5999.8132231517729</v>
-      </c>
-      <c r="M25" s="40"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="34"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="34">
+        <v>5999.81322315177</v>
+      </c>
+      <c r="M25" s="48"/>
+    </row>
+    <row r="26" spans="2:13">
+      <c r="B26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="44">
         <f t="shared" ref="E26:E39" si="10">$E$4</f>
         <v>6108.08</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="42">
         <f t="shared" si="6"/>
-        <v>1642.5474955466243</v>
-      </c>
-      <c r="I26" s="33">
+        <v>1642.54749554662</v>
+      </c>
+      <c r="I26" s="41">
         <v>33</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="42">
         <f t="shared" si="2"/>
-        <v>23.269422853577179</v>
-      </c>
-      <c r="K26" s="36">
+        <v>23.2694228535772</v>
+      </c>
+      <c r="K26" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="42">
         <f t="shared" si="3"/>
-        <v>6084.8105771464225</v>
-      </c>
-      <c r="M26" s="40"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="34"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34">
+        <v>6084.81057714642</v>
+      </c>
+      <c r="M26" s="48"/>
+    </row>
+    <row r="27" spans="2:13">
+      <c r="B27" s="42"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="42">
         <f t="shared" si="6"/>
-        <v>-4442.2630815997982</v>
-      </c>
-      <c r="I27" s="33">
+        <v>-4442.2630815998</v>
+      </c>
+      <c r="I27" s="41">
         <v>34</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="42">
         <f t="shared" si="2"/>
-        <v>-62.932060322663808</v>
-      </c>
-      <c r="K27" s="36">
+        <v>-62.9320603226638</v>
+      </c>
+      <c r="K27" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="42">
         <f t="shared" si="3"/>
-        <v>6171.0120603226642</v>
-      </c>
-      <c r="M27" s="40"/>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="34"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="34">
+        <v>6171.01206032266</v>
+      </c>
+      <c r="M27" s="48"/>
+    </row>
+    <row r="28" spans="2:13">
+      <c r="B28" s="42"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="42">
         <f t="shared" si="6"/>
-        <v>-10613.275141922462</v>
-      </c>
-      <c r="I28" s="33">
+        <v>-10613.2751419225</v>
+      </c>
+      <c r="I28" s="41">
         <v>35</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="42">
         <f t="shared" si="2"/>
-        <v>-150.3547311772349</v>
-      </c>
-      <c r="K28" s="36">
+        <v>-150.354731177235</v>
+      </c>
+      <c r="K28" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="42">
         <f t="shared" si="3"/>
-        <v>6258.4347311772344</v>
-      </c>
-      <c r="M28" s="40"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="34"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="34">
+        <v>6258.43473117723</v>
+      </c>
+      <c r="M28" s="48"/>
+    </row>
+    <row r="29" spans="2:13">
+      <c r="B29" s="42"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E29" s="36">
+      <c r="E29" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="42">
         <f t="shared" si="6"/>
-        <v>-16871.709873099695</v>
-      </c>
-      <c r="I29" s="33">
+        <v>-16871.7098730997</v>
+      </c>
+      <c r="I29" s="41">
         <v>36</v>
       </c>
-      <c r="J29" s="34">
+      <c r="J29" s="42">
         <f t="shared" si="2"/>
-        <v>-239.01588986891235</v>
-      </c>
-      <c r="K29" s="36">
+        <v>-239.015889868912</v>
+      </c>
+      <c r="K29" s="44">
         <f t="shared" si="7"/>
         <v>6108.08</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="42">
         <f t="shared" si="3"/>
-        <v>6347.0958898689123</v>
-      </c>
-      <c r="M29" s="40"/>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="34"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="34">
+        <v>6347.09588986891</v>
+      </c>
+      <c r="M29" s="48"/>
+    </row>
+    <row r="30" spans="2:13">
+      <c r="B30" s="42"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="34">
+      <c r="H30" s="42"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" s="36"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="40"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="34"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="34">
+      <c r="K30" s="44"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="48"/>
+    </row>
+    <row r="31" spans="2:13">
+      <c r="B31" s="42"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H31" s="34"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="34">
+      <c r="H31" s="42"/>
+      <c r="I31" s="41"/>
+      <c r="J31" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K31" s="36"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="40"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" s="34"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="34">
+      <c r="K31" s="44"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="48"/>
+    </row>
+    <row r="32" spans="2:13">
+      <c r="B32" s="42"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H32" s="34"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="34">
+      <c r="H32" s="42"/>
+      <c r="I32" s="41"/>
+      <c r="J32" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K32" s="36"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="40"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="34"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="34">
+      <c r="K32" s="44"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="48"/>
+    </row>
+    <row r="33" spans="2:13">
+      <c r="B33" s="42"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H33" s="34"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="34">
+      <c r="H33" s="42"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="40"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="34"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="34">
+      <c r="K33" s="44"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="48"/>
+    </row>
+    <row r="34" spans="2:13">
+      <c r="B34" s="42"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="34">
+      <c r="H34" s="42"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K34" s="36"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="40"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="34"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="34">
+      <c r="K34" s="44"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="48"/>
+    </row>
+    <row r="35" spans="2:13">
+      <c r="B35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="34">
+      <c r="H35" s="42"/>
+      <c r="I35" s="41"/>
+      <c r="J35" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="36"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="40"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="34"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="34">
+      <c r="K35" s="44"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="48"/>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="B36" s="42"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="34">
+      <c r="H36" s="42"/>
+      <c r="I36" s="41"/>
+      <c r="J36" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="36"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="40"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="34"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34">
+      <c r="K36" s="44"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="48"/>
+    </row>
+    <row r="37" spans="2:13">
+      <c r="B37" s="42"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E37" s="36">
+      <c r="E37" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="34">
+      <c r="H37" s="42"/>
+      <c r="I37" s="41"/>
+      <c r="J37" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="36"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="40"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="34"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="34">
+      <c r="K37" s="44"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="48"/>
+    </row>
+    <row r="38" spans="2:13">
+      <c r="B38" s="42"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="34">
+      <c r="H38" s="42"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K38" s="36"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="40"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="34"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="34">
+      <c r="K38" s="44"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="48"/>
+    </row>
+    <row r="39" spans="2:13">
+      <c r="B39" s="42"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="44">
         <f t="shared" si="10"/>
         <v>6108.08</v>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="42">
         <f t="shared" si="9"/>
         <v>6108.08</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="34">
+      <c r="H39" s="42"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="42">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K39" s="36"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="40"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="C41" s="33" t="s">
+      <c r="K39" s="44"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="48"/>
+    </row>
+    <row r="41" spans="3:10">
+      <c r="C41" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="42">
         <f>SUM(D4:D13)</f>
-        <v>27048.191155134762</v>
-      </c>
-      <c r="E41" s="25">
+        <v>27048.1911551348</v>
+      </c>
+      <c r="E41" s="33">
         <f>SUM(E4:E13)</f>
-        <v>61080.80000000001</v>
-      </c>
-      <c r="I41" s="33" t="s">
+        <v>61080.8</v>
+      </c>
+      <c r="I41" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="J41" s="34">
+      <c r="J41" s="42">
         <f>SUM(J4:J26)</f>
-        <v>20076.185763265214</v>
-      </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+        <v>20076.1857632652</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5">
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:5">
       <c r="E43" s="3">
         <f>E39*36</f>
         <v>219890.88</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:5">
       <c r="C44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="2:13" ht="57.6" x14ac:dyDescent="0.25">
+    <row r="45" ht="57.6" spans="3:6">
       <c r="C45" s="3"/>
       <c r="E45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F45" s="3">
         <f>E43-E41-H4</f>
-        <v>42842.688844864984</v>
-      </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+        <v>42842.688844865</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5">
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="2:13" ht="72" x14ac:dyDescent="0.25">
+    <row r="47" ht="72" spans="5:6">
       <c r="E47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F47" s="3">
         <f>E43-E41-H4-J41</f>
-        <v>22766.503081599771</v>
-      </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+        <v>22766.5030815998</v>
+      </c>
+    </row>
+    <row r="48" spans="5:5">
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:5">
       <c r="E49" s="3"/>
     </row>
   </sheetData>
@@ -3123,106 +3700,106 @@
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="N13:O20"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
-    <tabColor theme="3" tint="0.39994506668294322"/>
+    <tabColor theme="3" tint="0.399945066682943"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.4444444444444" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.44140625" style="1"/>
+    <col min="1" max="1" width="13.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.4444444444444" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1111111111111" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.4444444444444" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.4444444444444" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+    <row r="1" ht="25.5" customHeight="1" spans="1:7">
+      <c r="A1" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="57" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="57"/>
-    </row>
-    <row r="2" spans="1:7" ht="21.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="G1" s="27"/>
+    </row>
+    <row r="2" ht="21.9" customHeight="1" spans="1:7">
+      <c r="A2" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="29" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
-        <v>176284.79567514901</v>
-      </c>
-      <c r="B4" s="23">
+    <row r="4" spans="1:5">
+      <c r="A4" s="30">
+        <v>176284.795675149</v>
+      </c>
+      <c r="B4" s="31">
         <v>0.24</v>
       </c>
       <c r="C4" s="9">
         <v>12</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="30">
         <v>1</v>
       </c>
       <c r="E4" s="10">
         <f>A4*B4/C4*D4</f>
-        <v>3525.6959135029797</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
-        <v>176284.79567514901</v>
-      </c>
-      <c r="B5" s="23">
+        <v>3525.69591350298</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="30">
+        <v>176284.795675149</v>
+      </c>
+      <c r="B5" s="31">
         <v>0.17</v>
       </c>
       <c r="C5" s="9">
         <v>12</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="30">
         <v>1</v>
       </c>
       <c r="E5" s="10">
         <f>A5*B5/C5*D5</f>
-        <v>2497.3679387312777</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="24"/>
+        <v>2497.36793873128</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3230,32 +3807,33 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F1:G2"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="1"/>
-    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="1"/>
-    <col min="5" max="5" width="12.77734375" style="2" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.3333333333333" style="1"/>
+    <col min="3" max="3" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3333333333333" style="1"/>
+    <col min="5" max="5" width="12.7777777777778" style="2" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="12.7777777777778" style="3" customWidth="1"/>
     <col min="8" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="7.44140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.44444444444444" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.1111111111111" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.4444444444444" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:12">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>40</v>
@@ -3278,7 +3856,7 @@
       <c r="H1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="5" t="s">
         <v>47</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -3287,13 +3865,13 @@
       <c r="K1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
-        <v>52</v>
+    <row r="2" spans="1:12">
+      <c r="A2" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="B2" s="9">
         <f>客户方案计算表!E4*36</f>
@@ -3327,15 +3905,15 @@
       </c>
       <c r="K2" s="10">
         <f>客户方案计算表!D41+客户方案计算表!J41</f>
-        <v>47124.376918399976</v>
-      </c>
-      <c r="L2" s="18">
+        <v>47124.3769184</v>
+      </c>
+      <c r="L2" s="23">
         <f>B2-C2-K2</f>
-        <v>22766.503081600029</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+        <v>22766.5030816</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="12"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9"/>
@@ -3346,11 +3924,11 @@
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
-      <c r="L3" s="19"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="60" t="s">
-        <v>53</v>
+      <c r="L3" s="24"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="B4" s="9">
         <f>客户方案计算表!E4*36</f>
@@ -3384,326 +3962,326 @@
       </c>
       <c r="K4" s="10">
         <f>客户方案计算表!D41</f>
-        <v>27048.191155134762</v>
-      </c>
-      <c r="L4" s="18">
+        <v>27048.1911551348</v>
+      </c>
+      <c r="L4" s="23">
         <f>B4-C4-K4</f>
-        <v>42842.688844865246</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="20"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="62"/>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="62"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="62"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="62"/>
-      <c r="B8" s="62"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="62"/>
-      <c r="L8" s="62"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="62"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="62"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="62"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="62"/>
-    </row>
-    <row r="11" spans="1:12" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="62"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="s">
+        <v>42842.6888448652</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+    </row>
+    <row r="11" ht="84" customHeight="1" spans="1:12">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="58"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="58"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="59"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="59"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="59"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="59"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="59"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-    </row>
-    <row r="28" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+    </row>
+    <row r="28" ht="33" customHeight="1" spans="1:12">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3711,21 +4289,22 @@
     <mergeCell ref="A13:L20"/>
     <mergeCell ref="A22:L28"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="12.6640625"/>
+    <col min="7" max="7" width="12.6666666666667"/>
   </cols>
   <sheetData/>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>